--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128641175</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128641175</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128641175</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128641175</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128641175</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128641175</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128641175</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128641175</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128641175</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128641058</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>128641175</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>128641857</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128641058</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128641175</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,8 +1063,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128641857</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,62 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128641058</v>
+        <v>135746459</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>97511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Rullputt, Stora Rullputt, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516914</v>
+        <v>516889</v>
       </c>
       <c r="R2" t="n">
-        <v>6719123</v>
+        <v>6719127</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,81 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128641058</t>
+          <t>https://artportalen.se/Sighting/135746459</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128641175</v>
+        <v>135746854</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>97511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Rullputt, Stora Rullputt, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516907</v>
+        <v>516909</v>
       </c>
       <c r="R3" t="n">
-        <v>6719123</v>
+        <v>6719140</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,27 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Slutade räkna vid 100</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,71 +881,65 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128641175</t>
+          <t>https://artportalen.se/Sighting/135746854</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128641857</v>
+        <v>135744618</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>93345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516906</v>
+        <v>517001</v>
       </c>
       <c r="R4" t="n">
-        <v>6719121</v>
+        <v>6719084</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,27 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en yta av ca 0.5x 1.5 m finns grovat räknat 650 plantor, varierat tillstånd vara två stycken i blommning</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,18 +1008,3537 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135744618</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135747287</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>517007</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6719106</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135747287</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135745677</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516965</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6719113</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135745677</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135748102</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516910</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6719137</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135748102</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135749036</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516805</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6719186</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135749036</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135745780</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56920</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516931</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6719109</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135745780</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135744622</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>517001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6719083</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135744622</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135748847</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516803</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6719196</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tappad fjäder.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135748847</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135745214</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>517011</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6719094</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135745214</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135745296</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516994</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6719107</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135745296</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135745484</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516986</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6719108</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Inte purfärska men inte äldre heller.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135745484</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135745866</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516931</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6719119</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135745866</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135745876</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516930</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6719117</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135745876</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135746343</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516891</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6719128</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135746343</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135746497</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>516884</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6719139</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135746497</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135746577</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516884</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6719134</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135746577</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135747119</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>516985</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6719132</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135747119</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135747151</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516996</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6719123</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135747151</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135747233</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516997</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6719108</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135747233</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135747537</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>517007</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6719126</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135747537</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135747661</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>517010</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6719132</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135747661</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135747520</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>517008</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6719124</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135747520</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128641058</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>516914</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6719123</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128641058</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128641175</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>516907</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6719123</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Slutade räkna vid 100</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128641175</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128641857</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>516906</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6719121</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en yta av ca 0.5x 1.5 m finns grovat räknat 650 plantor, varierat tillstånd vara två stycken i blommning</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128641857</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135744170</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>516910</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6719111</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135744170</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135744239</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>516921</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6719107</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135744239</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135744844</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Iss klack, Iss klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>517038</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6719079</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Uppskattat minst 200, troligen långt mer, 12 i blom. Spridda över flera kvm.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135744844</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135746167</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>516908</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6719129</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bladrosetter spridda över större yta, 100+</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135746167</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135746331</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora Rullputt, Stora Rullputt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>516890</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6719127</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135746331</t>
         </is>
       </c>
     </row>
@@ -1074,6 +4547,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135746459</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135746854</v>
       </c>
       <c r="B3" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744618</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135747287</v>
       </c>
       <c r="B5" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135744170</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>135744239</v>
       </c>
       <c r="B30" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>135744844</v>
       </c>
       <c r="B31" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135746167</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>135746331</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135746459</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135746854</v>
       </c>
       <c r="B3" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744618</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135747287</v>
       </c>
       <c r="B5" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135745677</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>135748102</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135749036</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135745780</v>
       </c>
       <c r="B9" t="n">
-        <v>56920</v>
+        <v>56922</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135744622</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>135748847</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135745214</v>
       </c>
       <c r="B12" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>135745296</v>
       </c>
       <c r="B13" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135745484</v>
       </c>
       <c r="B14" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135745866</v>
       </c>
       <c r="B15" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135745876</v>
       </c>
       <c r="B16" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>135746343</v>
       </c>
       <c r="B17" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>135746497</v>
       </c>
       <c r="B18" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>135746577</v>
       </c>
       <c r="B19" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135747119</v>
       </c>
       <c r="B20" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135747151</v>
       </c>
       <c r="B21" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>135747233</v>
       </c>
       <c r="B22" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>135747537</v>
       </c>
       <c r="B23" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135747661</v>
       </c>
       <c r="B24" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135747520</v>
       </c>
       <c r="B25" t="n">
-        <v>58817</v>
+        <v>58819</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135744170</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>135744239</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>135744844</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135746167</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>135746331</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135746459</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135746854</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744618</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135747287</v>
       </c>
       <c r="B5" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135745677</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>135748102</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135749036</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135744170</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>135744239</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>135744844</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135746167</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>135746331</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135746459</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135746854</v>
       </c>
       <c r="B3" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744618</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135747287</v>
       </c>
       <c r="B5" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135744170</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>135744239</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>135744844</v>
       </c>
       <c r="B31" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135746167</v>
       </c>
       <c r="B32" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>135746331</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135746459</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135746854</v>
       </c>
       <c r="B3" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744618</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135747287</v>
       </c>
       <c r="B5" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135745677</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>135748102</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135749036</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135745780</v>
       </c>
       <c r="B9" t="n">
-        <v>56922</v>
+        <v>56923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135744622</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>135748847</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135747520</v>
       </c>
       <c r="B25" t="n">
-        <v>58819</v>
+        <v>58820</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135744170</v>
       </c>
       <c r="B29" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>135744239</v>
       </c>
       <c r="B30" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>135744844</v>
       </c>
       <c r="B31" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135746167</v>
       </c>
       <c r="B32" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>135746331</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135746459</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135746854</v>
       </c>
       <c r="B3" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744618</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135747287</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135745677</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>135748102</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135749036</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135745780</v>
       </c>
       <c r="B9" t="n">
-        <v>56923</v>
+        <v>56927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135744622</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>135748847</v>
       </c>
       <c r="B11" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135747520</v>
       </c>
       <c r="B25" t="n">
-        <v>58820</v>
+        <v>58824</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135744170</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>135744239</v>
       </c>
       <c r="B30" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>135744844</v>
       </c>
       <c r="B31" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135746167</v>
       </c>
       <c r="B32" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>135746331</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135746459</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135746854</v>
       </c>
       <c r="B3" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744618</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135747287</v>
       </c>
       <c r="B5" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135745677</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>135748102</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135749036</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135745780</v>
       </c>
       <c r="B9" t="n">
-        <v>56927</v>
+        <v>56928</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135744622</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>135748847</v>
       </c>
       <c r="B11" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135747520</v>
       </c>
       <c r="B25" t="n">
-        <v>58824</v>
+        <v>58825</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135744170</v>
       </c>
       <c r="B29" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>135744239</v>
       </c>
       <c r="B30" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>135744844</v>
       </c>
       <c r="B31" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135746167</v>
       </c>
       <c r="B32" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>135746331</v>
       </c>
       <c r="B33" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135746459</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135746854</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744618</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135747287</v>
       </c>
       <c r="B5" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135745677</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>135748102</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135749036</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135744170</v>
       </c>
       <c r="B29" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>135744239</v>
       </c>
       <c r="B30" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>135744844</v>
       </c>
       <c r="B31" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135746167</v>
       </c>
       <c r="B32" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>135746331</v>
       </c>
       <c r="B33" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 52613-2025 artfynd.xlsx
+++ b/artfynd/A 52613-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135746459</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135746854</v>
       </c>
       <c r="B3" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744618</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135747287</v>
       </c>
       <c r="B5" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135745677</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>135748102</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135749036</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135745780</v>
       </c>
       <c r="B9" t="n">
-        <v>56928</v>
+        <v>56933</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>135744622</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>135748847</v>
       </c>
       <c r="B11" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135747520</v>
       </c>
       <c r="B25" t="n">
-        <v>58825</v>
+        <v>58830</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135744170</v>
       </c>
       <c r="B29" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>135744239</v>
       </c>
       <c r="B30" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>135744844</v>
       </c>
       <c r="B31" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135746167</v>
       </c>
       <c r="B32" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>135746331</v>
       </c>
       <c r="B33" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
